--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-05.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-05.xlsx
@@ -474,751 +474,751 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583993425357</v>
+        <v>5583987180188</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Lucelia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sonia Maria Dantas de Sena</t>
+          <t>Lucelia dos Santos Costa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583988089729</v>
+        <v>5583996437484</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chesman</t>
+          <t>Pedro</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chesman Rodrigues</t>
+          <t>Pedro Henrick Ribeiro de Melo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583988115194</v>
+        <v>5583993425357</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gledson</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gledson Delgado da Silva</t>
+          <t>Sonia Maria Dantas de Sena</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583996382487</v>
+        <v>5583988089729</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Erick</t>
+          <t>Chesman</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Erick Santos Rufino da Silva</t>
+          <t>Chesman Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583982143996</v>
+        <v>5583988115194</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Elis</t>
+          <t>Gledson</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Elis Regina Franca de Castro</t>
+          <t>Gledson Delgado da Silva</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583991266589</v>
+        <v>5583996382487</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Erick</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Carlos Cesar Daniel dos Santos</t>
+          <t>Erick Santos Rufino da Silva</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583998270823</v>
+        <v>5583982143996</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Willamis</t>
+          <t>Elis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Willamis Raniere Faria Souza</t>
+          <t>Elis Regina Franca de Castro</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583986697764</v>
+        <v>5583991266589</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Joao</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Joao Vitor Sousa Alencar</t>
+          <t>Carlos Cesar Daniel dos Santos</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583988153069</v>
+        <v>5583998270823</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Elvis</t>
+          <t>Willamis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Elvis do Nascimento Guedes</t>
+          <t>Willamis Raniere Faria Souza</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583986921444</v>
+        <v>5583986697764</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fiderlandio</t>
+          <t>Joao</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fiderlandio de Sousa Silva</t>
+          <t>Joao Vitor Sousa Alencar</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583998695933</v>
+        <v>5583988153069</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ifbox</t>
+          <t>Elvis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ifbox Vidracaria</t>
+          <t>Elvis do Nascimento Guedes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583998275830</v>
+        <v>5583986921444</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Celia</t>
+          <t>Fiderlandio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Celia Freitas de Oliveira</t>
+          <t>Fiderlandio de Sousa Silva</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5521971474461</v>
+        <v>5583998695933</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mauro</t>
+          <t>Ifbox</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mauro Trajano</t>
+          <t>Ifbox Vidracaria</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583995822810</v>
+        <v>5583998275830</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Caixa</t>
+          <t>Celia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Caixa Escolar da Escola Municipal Americo Falcao</t>
+          <t>Celia Freitas de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583986592548</v>
+        <v>5521971474461</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Suellen</t>
+          <t>Mauro</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Suellen Regina da Silva Santos</t>
+          <t>Mauro Trajano</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583988165733</v>
+        <v>5583995822810</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ruana</t>
+          <t>Caixa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ruana Agra</t>
+          <t>Caixa Escolar da Escola Municipal Americo Falcao</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5583996503975</v>
+        <v>5583986592548</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Suellen</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Marcus Vinicius Albuquerque Santana</t>
+          <t>Suellen Regina da Silva Santos</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5561999621589</v>
+        <v>5583988165733</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Melksedec</t>
+          <t>Ruana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Melksedec de Araujo</t>
+          <t>Ruana Agra</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583999090945</v>
+        <v>5583996503975</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Edrienny</t>
+          <t>Marcus</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Edrienny Cinthya Alves de Lima</t>
+          <t>Marcus Vinicius Albuquerque Santana</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583988593255</v>
+        <v>5561999621589</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Manoel</t>
+          <t>Melksedec</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Manoel Tavares do Nascimento</t>
+          <t>Melksedec de Araujo</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583999857140</v>
+        <v>5583999090945</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Edrienny</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Marcus Jose de Lima Lobo</t>
+          <t>Edrienny Cinthya Alves de Lima</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583999393900</v>
+        <v>5583988593255</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Manoel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Maria de Fatima da Silva Dionisio</t>
+          <t>Manoel Tavares do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5583988269339</v>
+        <v>5583999857140</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>Marcus</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Francisco Vieira de Figueiredo</t>
+          <t>Marcus Jose de Lima Lobo</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583996016520</v>
+        <v>5583999393900</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lilo</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lilo</t>
+          <t>Maria de Fatima da Silva Dionisio</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5583988409781</v>
+        <v>5583988269339</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jackson Daniel Silva Silveira</t>
+          <t>Francisco Vieira de Figueiredo</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583981543987</v>
+        <v>5583996016520</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fabiano</t>
+          <t>Lilo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fabiano de Oliveira Silva</t>
+          <t>Lilo</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583988077231</v>
+        <v>5583988409781</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ytalo</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ytalo Marques Cassiano da Silva</t>
+          <t>Jackson Daniel Silva Silveira</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583986105972</v>
+        <v>5583981543987</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aristotelis</t>
+          <t>Fabiano</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Aristotelis Cesar Meneses Costa</t>
+          <t>Fabiano de Oliveira Silva</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583999787122</v>
+        <v>5583988077231</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Ytalo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fabio de Lima Thomaz</t>
+          <t>Ytalo Marques Cassiano da Silva</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5585981243458</v>
+        <v>5583986105972</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Antonia</t>
+          <t>Aristotelis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Antonia Rocha Pedrosa</t>
+          <t>Aristotelis Cesar Meneses Costa</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583988509085</v>
+        <v>5583999787122</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nathalia</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nathalia Ferreira da Silva</t>
+          <t>Fabio de Lima Thomaz</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5583999312401</v>
+        <v>5585981243458</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>Antonia</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Francisco Fernandes Vieira Ramos</t>
+          <t>Antonia Rocha Pedrosa</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583988719025</v>
+        <v>5583988509085</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Arthus</t>
+          <t>Nathalia</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Arthus de Brito Lima</t>
+          <t>Nathalia Ferreira da Silva</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583986574925</v>
+        <v>5583999312401</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wellington Rodolfo Gomes da Silva</t>
+          <t>Francisco Fernandes Vieira Ramos</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583998332102</v>
+        <v>5583988719025</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Edival</t>
+          <t>Arthus</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Edival Dantas</t>
+          <t>Arthus de Brito Lima</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5583999450229</v>
+        <v>5583986574925</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Francivaldo</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Francivaldo de Araujo Lima</t>
+          <t>Wellington Rodolfo Gomes da Silva</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583999465660</v>
+        <v>5583998332102</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sandro</t>
+          <t>Edival</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sandro Jose Vieira dos Santos</t>
+          <t>Edival Dantas</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583988853160</v>
+        <v>5583999450229</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Francivaldo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Marcos Vieira de Sousa</t>
+          <t>Francivaldo de Araujo Lima</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5583999441352</v>
+        <v>5583999465660</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Sandro</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jose Cleitiano</t>
+          <t>Sandro Jose Vieira dos Santos</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5583987965354</v>
+        <v>5583988853160</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Heliton</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Heliton Pedrosa de Melo</t>
+          <t>Marcos Vieira de Sousa</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583991116878</v>
+        <v>5583999441352</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mamede</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mamede Goncalves Saigg</t>
+          <t>Jose Cleitiano</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5584999951831</v>
+        <v>5584999711226</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Marilia</t>
+          <t>Infinity</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Marilia Gabriela Maia</t>
+          <t>Infinity At The Sea</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583988488173</v>
+        <v>5583987965354</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Suely</t>
+          <t>Heliton</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Suely Honorato Cantalice</t>
+          <t>Heliton Pedrosa de Melo</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5521983212365</v>
+        <v>5583991116878</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Josefa</t>
+          <t>Mamede</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Josefa Afonso Soares</t>
+          <t>Mamede Goncalves Saigg</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583981538056</v>
+        <v>5584999951831</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Marilia</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Casa Wert</t>
+          <t>Marilia Gabriela Maia</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583988635158</v>
+        <v>5583988488173</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Suely</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Angela Maria Marques Pereira</t>
+          <t>Suely Honorato Cantalice</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583988196881</v>
+        <v>5521983212365</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Josefa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Emerson Maciel Elias</t>
+          <t>Josefa Afonso Soares</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583988443608</v>
+        <v>5583981538056</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Edilson</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Edilson de Araujo Gomes</t>
+          <t>Casa Wert</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583994066976</v>
+        <v>5583988635158</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Incomel</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Incomel</t>
+          <t>Angela Maria Marques Pereira</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5581982200917</v>
+        <v>5583988196881</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ana Carolina dos Santos</t>
+          <t>Emerson Maciel Elias</t>
         </is>
       </c>
     </row>
